--- a/outputs/32902.xlsx
+++ b/outputs/32902.xlsx
@@ -413,15 +413,15 @@
         <v>65819</v>
       </c>
       <c r="C6" s="1" t="n">
-        <f aca="false">MAX(0,MIN(B6,90000)-60000)*0.15</f>
+        <f aca="false">MAX(0,MIN(65819,90000)-60000)*0.15</f>
         <v>872.85</v>
       </c>
       <c r="D6" s="1" t="n">
-        <f aca="false">MAX(0,MIN(B6,120000)-90000)*0.25</f>
+        <f aca="false">MAX(0,MIN(65819,120000)-90000)*0.25</f>
         <v>0</v>
       </c>
       <c r="E6" s="1" t="n">
-        <f aca="false">MAX(0,B6-120000)*0.35</f>
+        <f aca="false">MAX(0,65819-120000)*0.35</f>
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
@@ -437,15 +437,15 @@
         <v>30665</v>
       </c>
       <c r="C7" s="1" t="n">
-        <f aca="false">MAX(0,MIN(B7,90000)-60000)*0.15</f>
+        <f aca="false">MAX(0,MIN(30665,90000)-60000)*0.15</f>
         <v>0</v>
       </c>
       <c r="D7" s="1" t="n">
-        <f aca="false">MAX(0,MIN(B7,120000)-90000)*0.25</f>
+        <f aca="false">MAX(0,MIN(30665,120000)-90000)*0.25</f>
         <v>0</v>
       </c>
       <c r="E7" s="1" t="n">
-        <f aca="false">MAX(0,B7-120000)*0.35</f>
+        <f aca="false">MAX(0,30665-120000)*0.35</f>
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
@@ -461,15 +461,15 @@
         <v>131885</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">MAX(0,MIN(B8,90000)-60000)*0.15</f>
+        <f aca="false">MAX(0,MIN(131885,90000)-60000)*0.15</f>
         <v>4500</v>
       </c>
       <c r="D8" s="4" t="n">
-        <f aca="false">MAX(0,MIN(B8,120000)-90000)*0.25</f>
+        <f aca="false">MAX(0,MIN(131885,120000)-90000)*0.25</f>
         <v>7500</v>
       </c>
       <c r="E8" s="4" t="n">
-        <f aca="false">MAX(0,B8-120000)*0.35</f>
+        <f aca="false">MAX(0,131885-120000)*0.35</f>
         <v>4159.75</v>
       </c>
       <c r="F8" s="4" t="n">
@@ -485,15 +485,15 @@
         <v>25065</v>
       </c>
       <c r="C9" s="5" t="n">
-        <f aca="false">MAX(0,MIN(B9,90000)-60000)*0.15</f>
+        <f aca="false">MAX(0,MIN(25065,90000)-60000)*0.15</f>
         <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
-        <f aca="false">MAX(0,MIN(B9,120000)-90000)*0.25</f>
+        <f aca="false">MAX(0,MIN(25065,120000)-90000)*0.25</f>
         <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <f aca="false">MAX(0,B9-120000)*0.35</f>
+        <f aca="false">MAX(0,25065-120000)*0.35</f>
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
